--- a/backend/data/financials_by_company/0146.HK.xlsx
+++ b/backend/data/financials_by_company/0146.HK.xlsx
@@ -657,58 +657,58 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>-762754.771072</v>
+        <v>-361680</v>
       </c>
       <c r="C2" t="n">
-        <v>0.118754</v>
+        <v>0.165</v>
       </c>
       <c r="D2" t="n">
-        <v>104838000</v>
+        <v>80695000</v>
       </c>
       <c r="E2" t="n">
-        <v>-6423000</v>
+        <v>-2192000</v>
       </c>
       <c r="F2" t="n">
-        <v>-6423000</v>
+        <v>-2192000</v>
       </c>
       <c r="G2" t="n">
-        <v>42113000</v>
+        <v>16634000</v>
       </c>
       <c r="H2" t="n">
-        <v>46366000</v>
+        <v>58459000</v>
       </c>
       <c r="I2" t="n">
-        <v>245202000</v>
+        <v>201277000</v>
       </c>
       <c r="J2" t="n">
-        <v>98415000</v>
+        <v>78503000</v>
       </c>
       <c r="K2" t="n">
-        <v>52049000</v>
+        <v>20044000</v>
       </c>
       <c r="L2" t="n">
-        <v>2231000</v>
+        <v>-2569000</v>
       </c>
       <c r="M2" t="n">
-        <v>4261000</v>
+        <v>3496000</v>
       </c>
       <c r="N2" t="n">
-        <v>6492000</v>
+        <v>927000</v>
       </c>
       <c r="O2" t="n">
-        <v>47773245.228928</v>
+        <v>18464320</v>
       </c>
       <c r="P2" t="n">
-        <v>42113000</v>
+        <v>16634000</v>
       </c>
       <c r="Q2" t="n">
-        <v>592208000</v>
+        <v>463389000</v>
       </c>
       <c r="R2" t="n">
-        <v>45557000</v>
+        <v>19117000</v>
       </c>
       <c r="S2" t="n">
         <v>212187000</v>
@@ -717,139 +717,141 @@
         <v>212187000</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1985</v>
+        <v>0.0784</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1985</v>
+        <v>0.0784</v>
       </c>
       <c r="W2" t="n">
-        <v>42113000</v>
+        <v>16634000</v>
       </c>
       <c r="X2" t="n">
-        <v>42113000</v>
+        <v>16634000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>42113000</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
+        <v>16634000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
       <c r="AB2" t="n">
-        <v>42113000</v>
+        <v>16634000</v>
       </c>
       <c r="AC2" t="n">
-        <v>42113000</v>
+        <v>16634000</v>
       </c>
       <c r="AD2" t="n">
-        <v>5675000</v>
+        <v>-86000</v>
       </c>
       <c r="AE2" t="n">
-        <v>47788000</v>
+        <v>16548000</v>
       </c>
       <c r="AF2" t="n">
-        <v>4654000</v>
+        <v>4345000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-6423000</v>
+        <v>-3576000</v>
       </c>
       <c r="AH2" t="n">
-        <v>6423000</v>
+        <v>-6818000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>10394000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2231000</v>
+        <v>-2569000</v>
       </c>
       <c r="AK2" t="n">
-        <v>4261000</v>
+        <v>3496000</v>
       </c>
       <c r="AL2" t="n">
-        <v>6492000</v>
+        <v>927000</v>
       </c>
       <c r="AM2" t="n">
-        <v>48007000</v>
+        <v>17990000</v>
       </c>
       <c r="AN2" t="n">
-        <v>347006000</v>
+        <v>262112000</v>
       </c>
       <c r="AO2" t="n">
-        <v>347006000</v>
+        <v>262112000</v>
       </c>
       <c r="AP2" t="n">
-        <v>189040000</v>
+        <v>135063000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>157966000</v>
+        <v>127049000</v>
       </c>
       <c r="AR2" t="n">
-        <v>395013000</v>
+        <v>280102000</v>
       </c>
       <c r="AS2" t="n">
-        <v>245202000</v>
+        <v>201277000</v>
       </c>
       <c r="AT2" t="n">
-        <v>640215000</v>
+        <v>481379000</v>
       </c>
       <c r="AU2" t="n">
-        <v>640215000</v>
+        <v>481379000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>-73026.092172</v>
+        <v>103432.453946</v>
       </c>
       <c r="C3" t="n">
-        <v>0.039688</v>
+        <v>0.04196</v>
       </c>
       <c r="D3" t="n">
-        <v>94543000</v>
+        <v>80640000</v>
       </c>
       <c r="E3" t="n">
-        <v>-1840000</v>
+        <v>2465000</v>
       </c>
       <c r="F3" t="n">
-        <v>-1840000</v>
+        <v>2465000</v>
       </c>
       <c r="G3" t="n">
-        <v>38424000</v>
+        <v>25275000</v>
       </c>
       <c r="H3" t="n">
-        <v>49285000</v>
+        <v>53803000</v>
       </c>
       <c r="I3" t="n">
-        <v>240682000</v>
+        <v>252837000</v>
       </c>
       <c r="J3" t="n">
-        <v>92703000</v>
+        <v>83105000</v>
       </c>
       <c r="K3" t="n">
-        <v>43418000</v>
+        <v>29302000</v>
       </c>
       <c r="L3" t="n">
-        <v>85000</v>
+        <v>-1756000</v>
       </c>
       <c r="M3" t="n">
-        <v>3406000</v>
+        <v>2920000</v>
       </c>
       <c r="N3" t="n">
-        <v>3491000</v>
+        <v>1164000</v>
       </c>
       <c r="O3" t="n">
-        <v>40190973.907828</v>
+        <v>22913432.453946</v>
       </c>
       <c r="P3" t="n">
-        <v>38424000</v>
+        <v>25275000</v>
       </c>
       <c r="Q3" t="n">
-        <v>567195000</v>
+        <v>562807000</v>
       </c>
       <c r="R3" t="n">
-        <v>39927000</v>
+        <v>28138000</v>
       </c>
       <c r="S3" t="n">
         <v>212187000</v>
@@ -858,139 +860,139 @@
         <v>212187000</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1811</v>
+        <v>0.1191</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1811</v>
+        <v>0.1191</v>
       </c>
       <c r="W3" t="n">
-        <v>38424000</v>
+        <v>25275000</v>
       </c>
       <c r="X3" t="n">
-        <v>38424000</v>
+        <v>25275000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>38424000</v>
+        <v>25275000</v>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>38424000</v>
+        <v>25275000</v>
       </c>
       <c r="AC3" t="n">
-        <v>38424000</v>
+        <v>25275000</v>
       </c>
       <c r="AD3" t="n">
-        <v>1588000</v>
+        <v>1107000</v>
       </c>
       <c r="AE3" t="n">
-        <v>40012000</v>
+        <v>26382000</v>
       </c>
       <c r="AF3" t="n">
-        <v>5065000</v>
+        <v>5242000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-1261000</v>
+        <v>-1420000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-86000</v>
+        <v>11000</v>
       </c>
       <c r="AI3" t="n">
-        <v>1347000</v>
+        <v>1409000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>85000</v>
+        <v>-1756000</v>
       </c>
       <c r="AK3" t="n">
-        <v>3406000</v>
+        <v>2920000</v>
       </c>
       <c r="AL3" t="n">
-        <v>3491000</v>
+        <v>1164000</v>
       </c>
       <c r="AM3" t="n">
-        <v>33401000</v>
+        <v>20849000</v>
       </c>
       <c r="AN3" t="n">
-        <v>326513000</v>
+        <v>309970000</v>
       </c>
       <c r="AO3" t="n">
-        <v>326513000</v>
+        <v>309970000</v>
       </c>
       <c r="AP3" t="n">
-        <v>167285000</v>
+        <v>162529000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>159228000</v>
+        <v>147441000</v>
       </c>
       <c r="AR3" t="n">
-        <v>359914000</v>
+        <v>330819000</v>
       </c>
       <c r="AS3" t="n">
-        <v>240682000</v>
+        <v>252837000</v>
       </c>
       <c r="AT3" t="n">
-        <v>600596000</v>
+        <v>583656000</v>
       </c>
       <c r="AU3" t="n">
-        <v>600596000</v>
+        <v>583656000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>103432.453946</v>
+        <v>-73026.092172</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04196</v>
+        <v>0.039688</v>
       </c>
       <c r="D4" t="n">
-        <v>80640000</v>
+        <v>94543000</v>
       </c>
       <c r="E4" t="n">
-        <v>2465000</v>
+        <v>-1840000</v>
       </c>
       <c r="F4" t="n">
-        <v>2465000</v>
+        <v>-1840000</v>
       </c>
       <c r="G4" t="n">
-        <v>25275000</v>
+        <v>38424000</v>
       </c>
       <c r="H4" t="n">
-        <v>53803000</v>
+        <v>49285000</v>
       </c>
       <c r="I4" t="n">
-        <v>252837000</v>
+        <v>240682000</v>
       </c>
       <c r="J4" t="n">
-        <v>83105000</v>
+        <v>92703000</v>
       </c>
       <c r="K4" t="n">
-        <v>29302000</v>
+        <v>43418000</v>
       </c>
       <c r="L4" t="n">
-        <v>-1756000</v>
+        <v>85000</v>
       </c>
       <c r="M4" t="n">
-        <v>2920000</v>
+        <v>3406000</v>
       </c>
       <c r="N4" t="n">
-        <v>1164000</v>
+        <v>3491000</v>
       </c>
       <c r="O4" t="n">
-        <v>22913432.453946</v>
+        <v>40190973.907828</v>
       </c>
       <c r="P4" t="n">
-        <v>25275000</v>
+        <v>38424000</v>
       </c>
       <c r="Q4" t="n">
-        <v>562807000</v>
+        <v>567195000</v>
       </c>
       <c r="R4" t="n">
-        <v>28138000</v>
+        <v>39927000</v>
       </c>
       <c r="S4" t="n">
         <v>212187000</v>
@@ -999,139 +1001,139 @@
         <v>212187000</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1191</v>
+        <v>0.1811</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1191</v>
+        <v>0.1811</v>
       </c>
       <c r="W4" t="n">
-        <v>25275000</v>
+        <v>38424000</v>
       </c>
       <c r="X4" t="n">
-        <v>25275000</v>
+        <v>38424000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>25275000</v>
+        <v>38424000</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>25275000</v>
+        <v>38424000</v>
       </c>
       <c r="AC4" t="n">
-        <v>25275000</v>
+        <v>38424000</v>
       </c>
       <c r="AD4" t="n">
-        <v>1107000</v>
+        <v>1588000</v>
       </c>
       <c r="AE4" t="n">
-        <v>26382000</v>
+        <v>40012000</v>
       </c>
       <c r="AF4" t="n">
-        <v>5242000</v>
+        <v>5065000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1420000</v>
+        <v>-1261000</v>
       </c>
       <c r="AH4" t="n">
-        <v>11000</v>
+        <v>-86000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1409000</v>
+        <v>1347000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-1756000</v>
+        <v>85000</v>
       </c>
       <c r="AK4" t="n">
-        <v>2920000</v>
+        <v>3406000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1164000</v>
+        <v>3491000</v>
       </c>
       <c r="AM4" t="n">
-        <v>20849000</v>
+        <v>33401000</v>
       </c>
       <c r="AN4" t="n">
-        <v>309970000</v>
+        <v>326513000</v>
       </c>
       <c r="AO4" t="n">
-        <v>309970000</v>
+        <v>326513000</v>
       </c>
       <c r="AP4" t="n">
-        <v>162529000</v>
+        <v>167285000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>147441000</v>
+        <v>159228000</v>
       </c>
       <c r="AR4" t="n">
-        <v>330819000</v>
+        <v>359914000</v>
       </c>
       <c r="AS4" t="n">
-        <v>252837000</v>
+        <v>240682000</v>
       </c>
       <c r="AT4" t="n">
-        <v>583656000</v>
+        <v>600596000</v>
       </c>
       <c r="AU4" t="n">
-        <v>583656000</v>
+        <v>600596000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>-361680</v>
+        <v>-762754.771072</v>
       </c>
       <c r="C5" t="n">
-        <v>0.165</v>
+        <v>0.118754</v>
       </c>
       <c r="D5" t="n">
-        <v>80695000</v>
+        <v>104838000</v>
       </c>
       <c r="E5" t="n">
-        <v>-2192000</v>
+        <v>-6423000</v>
       </c>
       <c r="F5" t="n">
-        <v>-2192000</v>
+        <v>-6423000</v>
       </c>
       <c r="G5" t="n">
-        <v>16634000</v>
+        <v>42113000</v>
       </c>
       <c r="H5" t="n">
-        <v>58459000</v>
+        <v>46366000</v>
       </c>
       <c r="I5" t="n">
-        <v>201277000</v>
+        <v>245202000</v>
       </c>
       <c r="J5" t="n">
-        <v>78503000</v>
+        <v>98415000</v>
       </c>
       <c r="K5" t="n">
-        <v>20044000</v>
+        <v>52049000</v>
       </c>
       <c r="L5" t="n">
-        <v>-2569000</v>
+        <v>2231000</v>
       </c>
       <c r="M5" t="n">
-        <v>3496000</v>
+        <v>4261000</v>
       </c>
       <c r="N5" t="n">
-        <v>927000</v>
+        <v>6492000</v>
       </c>
       <c r="O5" t="n">
-        <v>18464320</v>
+        <v>47773245.228928</v>
       </c>
       <c r="P5" t="n">
-        <v>16634000</v>
+        <v>42113000</v>
       </c>
       <c r="Q5" t="n">
-        <v>463389000</v>
+        <v>592208000</v>
       </c>
       <c r="R5" t="n">
-        <v>19117000</v>
+        <v>45557000</v>
       </c>
       <c r="S5" t="n">
         <v>212187000</v>
@@ -1140,85 +1142,83 @@
         <v>212187000</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0784</v>
+        <v>0.1985</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0784</v>
+        <v>0.1985</v>
       </c>
       <c r="W5" t="n">
-        <v>16634000</v>
+        <v>42113000</v>
       </c>
       <c r="X5" t="n">
-        <v>16634000</v>
+        <v>42113000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>16634000</v>
-      </c>
-      <c r="AA5" t="n">
+        <v>42113000</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="n">
+        <v>42113000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>42113000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>5675000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>47788000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>4654000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-6423000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>6423000</v>
+      </c>
+      <c r="AI5" t="n">
         <v>0</v>
       </c>
-      <c r="AB5" t="n">
-        <v>16634000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>16634000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-86000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>16548000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>4345000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-3576000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-6818000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>10394000</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>-2569000</v>
+        <v>2231000</v>
       </c>
       <c r="AK5" t="n">
-        <v>3496000</v>
+        <v>4261000</v>
       </c>
       <c r="AL5" t="n">
-        <v>927000</v>
+        <v>6492000</v>
       </c>
       <c r="AM5" t="n">
-        <v>17990000</v>
+        <v>48007000</v>
       </c>
       <c r="AN5" t="n">
-        <v>262112000</v>
+        <v>347006000</v>
       </c>
       <c r="AO5" t="n">
-        <v>262112000</v>
+        <v>347006000</v>
       </c>
       <c r="AP5" t="n">
-        <v>135063000</v>
+        <v>189040000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>127049000</v>
+        <v>157966000</v>
       </c>
       <c r="AR5" t="n">
-        <v>280102000</v>
+        <v>395013000</v>
       </c>
       <c r="AS5" t="n">
-        <v>201277000</v>
+        <v>245202000</v>
       </c>
       <c r="AT5" t="n">
-        <v>481379000</v>
+        <v>640215000</v>
       </c>
       <c r="AU5" t="n">
-        <v>481379000</v>
+        <v>640215000</v>
       </c>
     </row>
   </sheetData>
@@ -1569,7 +1569,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
         <v>212187488</v>
@@ -1578,43 +1578,45 @@
         <v>212187488</v>
       </c>
       <c r="D2" t="n">
-        <v>114257000</v>
+        <v>129366000</v>
       </c>
       <c r="E2" t="n">
-        <v>421892000</v>
+        <v>380076000</v>
       </c>
       <c r="F2" t="n">
-        <v>454940000</v>
+        <v>440303000</v>
       </c>
       <c r="G2" t="n">
-        <v>130391000</v>
+        <v>27219000</v>
       </c>
       <c r="H2" t="n">
-        <v>421892000</v>
+        <v>380076000</v>
       </c>
       <c r="I2" t="n">
-        <v>114257000</v>
+        <v>113846000</v>
       </c>
       <c r="J2" t="n">
-        <v>454940000</v>
+        <v>424783000</v>
       </c>
       <c r="K2" t="n">
-        <v>454940000</v>
+        <v>424783000</v>
       </c>
       <c r="L2" t="n">
-        <v>454940000</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
+        <v>424783000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
       <c r="N2" t="n">
-        <v>454940000</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
+        <v>424783000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>6366000</v>
+      </c>
       <c r="P2" t="n">
-        <v>193160000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>189699000</v>
-      </c>
+        <v>125729000</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
         <v>21219000</v>
       </c>
@@ -1622,149 +1624,145 @@
         <v>21219000</v>
       </c>
       <c r="T2" t="n">
-        <v>377626000</v>
+        <v>360094000</v>
       </c>
       <c r="U2" t="n">
-        <v>94838000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>262000</v>
-      </c>
+        <v>93297000</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>5014000</v>
+        <v>3738000</v>
       </c>
       <c r="X2" t="n">
-        <v>1242000</v>
+        <v>1570000</v>
       </c>
       <c r="Y2" t="n">
-        <v>88320000</v>
+        <v>87989000</v>
       </c>
       <c r="Z2" t="n">
-        <v>88320000</v>
+        <v>87989000</v>
       </c>
       <c r="AA2" t="n">
-        <v>282788000</v>
+        <v>266797000</v>
       </c>
       <c r="AB2" t="n">
-        <v>25937000</v>
+        <v>41377000</v>
       </c>
       <c r="AC2" t="n">
-        <v>25937000</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
+        <v>25857000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>15520000</v>
+      </c>
       <c r="AE2" t="n">
-        <v>80211000</v>
+        <v>58308000</v>
       </c>
       <c r="AF2" t="n">
-        <v>38472000</v>
+        <v>35748000</v>
       </c>
       <c r="AG2" t="n">
-        <v>8236000</v>
+        <v>2893000</v>
       </c>
       <c r="AH2" t="n">
-        <v>33503000</v>
+        <v>19667000</v>
       </c>
       <c r="AI2" t="n">
-        <v>832566000</v>
+        <v>784877000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>419387000</v>
+        <v>490861000</v>
       </c>
       <c r="AK2" t="n">
-        <v>8094000</v>
+        <v>2698000</v>
       </c>
       <c r="AL2" t="n">
-        <v>70077000</v>
+        <v>82976000</v>
       </c>
       <c r="AM2" t="n">
-        <v>33048000</v>
+        <v>44707000</v>
       </c>
       <c r="AN2" t="n">
-        <v>33048000</v>
+        <v>44707000</v>
       </c>
       <c r="AO2" t="n">
-        <v>301986000</v>
+        <v>355024000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-276387000</v>
+        <v>-286148000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>578373000</v>
+        <v>641172000</v>
       </c>
       <c r="AR2" t="n">
-        <v>270000</v>
+        <v>89000</v>
       </c>
       <c r="AS2" t="n">
-        <v>1261000</v>
+        <v>1155000</v>
       </c>
       <c r="AT2" t="n">
-        <v>152643000</v>
+        <v>184947000</v>
       </c>
       <c r="AU2" t="n">
-        <v>424199000</v>
+        <v>454981000</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>413179000</v>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+        <v>294016000</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>550000</v>
+      </c>
       <c r="AY2" t="n">
-        <v>641000</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6011000</v>
+        <v>12411000</v>
       </c>
       <c r="BA2" t="n">
-        <v>49515000</v>
+        <v>51306000</v>
       </c>
       <c r="BB2" t="n">
-        <v>-31899000</v>
+        <v>-15809000</v>
       </c>
       <c r="BC2" t="n">
-        <v>48659000</v>
+        <v>28192000</v>
       </c>
       <c r="BD2" t="n">
-        <v>5715000</v>
+        <v>6956000</v>
       </c>
       <c r="BE2" t="n">
-        <v>27040000</v>
+        <v>31967000</v>
       </c>
       <c r="BF2" t="n">
-        <v>18773000</v>
+        <v>7820000</v>
       </c>
       <c r="BG2" t="n">
-        <v>623000</v>
+        <v>6532000</v>
       </c>
       <c r="BH2" t="n">
-        <v>72030000</v>
+        <v>36141000</v>
       </c>
       <c r="BI2" t="n">
-        <v>-7749000</v>
+        <v>-3541000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>79779000</v>
+        <v>39682000</v>
       </c>
       <c r="BK2" t="n">
-        <v>263323000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>129551000</v>
-      </c>
+        <v>178173000</v>
+      </c>
+      <c r="BL2" t="inlineStr"/>
       <c r="BM2" t="n">
-        <v>133772000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>105592000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>28180000</v>
-      </c>
+        <v>178173000</v>
+      </c>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
         <v>212187488</v>
@@ -1773,41 +1771,41 @@
         <v>212187488</v>
       </c>
       <c r="D3" t="n">
-        <v>124118000</v>
+        <v>107215000</v>
       </c>
       <c r="E3" t="n">
-        <v>392893000</v>
+        <v>387959000</v>
       </c>
       <c r="F3" t="n">
-        <v>428594000</v>
+        <v>429131000</v>
       </c>
       <c r="G3" t="n">
-        <v>95880000</v>
+        <v>62041000</v>
       </c>
       <c r="H3" t="n">
-        <v>392893000</v>
+        <v>387959000</v>
       </c>
       <c r="I3" t="n">
-        <v>124118000</v>
+        <v>107215000</v>
       </c>
       <c r="J3" t="n">
-        <v>428594000</v>
+        <v>429131000</v>
       </c>
       <c r="K3" t="n">
-        <v>428594000</v>
+        <v>429131000</v>
       </c>
       <c r="L3" t="n">
-        <v>428594000</v>
+        <v>429131000</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>428594000</v>
+        <v>429131000</v>
       </c>
       <c r="O3" t="n">
-        <v>19097000</v>
+        <v>12731000</v>
       </c>
       <c r="P3" t="n">
-        <v>170402000</v>
+        <v>144672000</v>
       </c>
       <c r="Q3" t="n">
         <v>189699000</v>
@@ -1819,147 +1817,151 @@
         <v>21219000</v>
       </c>
       <c r="T3" t="n">
-        <v>364273000</v>
+        <v>358878000</v>
       </c>
       <c r="U3" t="n">
-        <v>103316000</v>
+        <v>87614000</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>4161000</v>
+        <v>3623000</v>
       </c>
       <c r="X3" t="n">
-        <v>1380000</v>
+        <v>1539000</v>
       </c>
       <c r="Y3" t="n">
-        <v>97775000</v>
+        <v>82452000</v>
       </c>
       <c r="Z3" t="n">
-        <v>97775000</v>
+        <v>82452000</v>
       </c>
       <c r="AA3" t="n">
-        <v>260957000</v>
+        <v>271264000</v>
       </c>
       <c r="AB3" t="n">
-        <v>26343000</v>
+        <v>24763000</v>
       </c>
       <c r="AC3" t="n">
-        <v>26343000</v>
-      </c>
-      <c r="AD3" t="inlineStr"/>
+        <v>24763000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
       <c r="AE3" t="n">
-        <v>69080000</v>
+        <v>70887000</v>
       </c>
       <c r="AF3" t="n">
-        <v>35830000</v>
+        <v>36021000</v>
       </c>
       <c r="AG3" t="n">
-        <v>4092000</v>
+        <v>3518000</v>
       </c>
       <c r="AH3" t="n">
-        <v>29158000</v>
+        <v>31348000</v>
       </c>
       <c r="AI3" t="n">
-        <v>792867000</v>
+        <v>788009000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>436030000</v>
+        <v>454704000</v>
       </c>
       <c r="AK3" t="n">
-        <v>4187000</v>
+        <v>3823000</v>
       </c>
       <c r="AL3" t="n">
-        <v>71192000</v>
+        <v>78720000</v>
       </c>
       <c r="AM3" t="n">
-        <v>35701000</v>
+        <v>41172000</v>
       </c>
       <c r="AN3" t="n">
-        <v>35701000</v>
+        <v>41172000</v>
       </c>
       <c r="AO3" t="n">
-        <v>324950000</v>
+        <v>330989000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-278526000</v>
+        <v>-262989000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>603476000</v>
+        <v>593978000</v>
       </c>
       <c r="AR3" t="n">
-        <v>270000</v>
+        <v>545000</v>
       </c>
       <c r="AS3" t="n">
-        <v>1243000</v>
+        <v>688000</v>
       </c>
       <c r="AT3" t="n">
-        <v>157259000</v>
+        <v>177081000</v>
       </c>
       <c r="AU3" t="n">
-        <v>444704000</v>
+        <v>415664000</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>356837000</v>
+        <v>333305000</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1783000</v>
       </c>
       <c r="AY3" t="n">
-        <v>615000</v>
+        <v>413000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12410000</v>
+        <v>12848000</v>
       </c>
       <c r="BA3" t="n">
-        <v>46418000</v>
+        <v>57656000</v>
       </c>
       <c r="BB3" t="n">
-        <v>-25274000</v>
+        <v>-18000000</v>
       </c>
       <c r="BC3" t="n">
-        <v>38745000</v>
+        <v>38879000</v>
       </c>
       <c r="BD3" t="n">
-        <v>5194000</v>
+        <v>7912000</v>
       </c>
       <c r="BE3" t="n">
-        <v>27753000</v>
+        <v>28865000</v>
       </c>
       <c r="BF3" t="n">
-        <v>15114000</v>
+        <v>11409000</v>
       </c>
       <c r="BG3" t="n">
-        <v>1180000</v>
+        <v>4168000</v>
       </c>
       <c r="BH3" t="n">
-        <v>63443000</v>
+        <v>49069000</v>
       </c>
       <c r="BI3" t="n">
-        <v>-6657000</v>
+        <v>-5215000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>70100000</v>
+        <v>54284000</v>
       </c>
       <c r="BK3" t="n">
-        <v>217657000</v>
-      </c>
-      <c r="BL3" t="inlineStr"/>
+        <v>195959000</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>32941000</v>
+      </c>
       <c r="BM3" t="n">
-        <v>217657000</v>
+        <v>163018000</v>
       </c>
       <c r="BN3" t="n">
-        <v>196985000</v>
+        <v>129964000</v>
       </c>
       <c r="BO3" t="n">
-        <v>20672000</v>
+        <v>33054000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
         <v>212187488</v>
@@ -1968,41 +1970,41 @@
         <v>212187488</v>
       </c>
       <c r="D4" t="n">
-        <v>107215000</v>
+        <v>124118000</v>
       </c>
       <c r="E4" t="n">
-        <v>387959000</v>
+        <v>392893000</v>
       </c>
       <c r="F4" t="n">
-        <v>429131000</v>
+        <v>428594000</v>
       </c>
       <c r="G4" t="n">
-        <v>62041000</v>
+        <v>95880000</v>
       </c>
       <c r="H4" t="n">
-        <v>387959000</v>
+        <v>392893000</v>
       </c>
       <c r="I4" t="n">
-        <v>107215000</v>
+        <v>124118000</v>
       </c>
       <c r="J4" t="n">
-        <v>429131000</v>
+        <v>428594000</v>
       </c>
       <c r="K4" t="n">
-        <v>429131000</v>
+        <v>428594000</v>
       </c>
       <c r="L4" t="n">
-        <v>429131000</v>
+        <v>428594000</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>429131000</v>
+        <v>428594000</v>
       </c>
       <c r="O4" t="n">
-        <v>12731000</v>
+        <v>19097000</v>
       </c>
       <c r="P4" t="n">
-        <v>144672000</v>
+        <v>170402000</v>
       </c>
       <c r="Q4" t="n">
         <v>189699000</v>
@@ -2014,151 +2016,147 @@
         <v>21219000</v>
       </c>
       <c r="T4" t="n">
-        <v>358878000</v>
+        <v>364273000</v>
       </c>
       <c r="U4" t="n">
-        <v>87614000</v>
+        <v>103316000</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>3623000</v>
+        <v>4161000</v>
       </c>
       <c r="X4" t="n">
-        <v>1539000</v>
+        <v>1380000</v>
       </c>
       <c r="Y4" t="n">
-        <v>82452000</v>
+        <v>97775000</v>
       </c>
       <c r="Z4" t="n">
-        <v>82452000</v>
+        <v>97775000</v>
       </c>
       <c r="AA4" t="n">
-        <v>271264000</v>
+        <v>260957000</v>
       </c>
       <c r="AB4" t="n">
-        <v>24763000</v>
+        <v>26343000</v>
       </c>
       <c r="AC4" t="n">
-        <v>24763000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
+        <v>26343000</v>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>70887000</v>
+        <v>69080000</v>
       </c>
       <c r="AF4" t="n">
-        <v>36021000</v>
+        <v>35830000</v>
       </c>
       <c r="AG4" t="n">
-        <v>3518000</v>
+        <v>4092000</v>
       </c>
       <c r="AH4" t="n">
-        <v>31348000</v>
+        <v>29158000</v>
       </c>
       <c r="AI4" t="n">
-        <v>788009000</v>
+        <v>792867000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>454704000</v>
+        <v>436030000</v>
       </c>
       <c r="AK4" t="n">
-        <v>3823000</v>
+        <v>4187000</v>
       </c>
       <c r="AL4" t="n">
-        <v>78720000</v>
+        <v>71192000</v>
       </c>
       <c r="AM4" t="n">
-        <v>41172000</v>
+        <v>35701000</v>
       </c>
       <c r="AN4" t="n">
-        <v>41172000</v>
+        <v>35701000</v>
       </c>
       <c r="AO4" t="n">
-        <v>330989000</v>
+        <v>324950000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-262989000</v>
+        <v>-278526000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>593978000</v>
+        <v>603476000</v>
       </c>
       <c r="AR4" t="n">
-        <v>545000</v>
+        <v>270000</v>
       </c>
       <c r="AS4" t="n">
-        <v>688000</v>
+        <v>1243000</v>
       </c>
       <c r="AT4" t="n">
-        <v>177081000</v>
+        <v>157259000</v>
       </c>
       <c r="AU4" t="n">
-        <v>415664000</v>
+        <v>444704000</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>333305000</v>
+        <v>356837000</v>
       </c>
       <c r="AX4" t="n">
-        <v>1783000</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>413000</v>
+        <v>615000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12848000</v>
+        <v>12410000</v>
       </c>
       <c r="BA4" t="n">
-        <v>57656000</v>
+        <v>46418000</v>
       </c>
       <c r="BB4" t="n">
-        <v>-18000000</v>
+        <v>-25274000</v>
       </c>
       <c r="BC4" t="n">
-        <v>38879000</v>
+        <v>38745000</v>
       </c>
       <c r="BD4" t="n">
-        <v>7912000</v>
+        <v>5194000</v>
       </c>
       <c r="BE4" t="n">
-        <v>28865000</v>
+        <v>27753000</v>
       </c>
       <c r="BF4" t="n">
-        <v>11409000</v>
+        <v>15114000</v>
       </c>
       <c r="BG4" t="n">
-        <v>4168000</v>
+        <v>1180000</v>
       </c>
       <c r="BH4" t="n">
-        <v>49069000</v>
+        <v>63443000</v>
       </c>
       <c r="BI4" t="n">
-        <v>-5215000</v>
+        <v>-6657000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>54284000</v>
+        <v>70100000</v>
       </c>
       <c r="BK4" t="n">
-        <v>195959000</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>32941000</v>
-      </c>
+        <v>217657000</v>
+      </c>
+      <c r="BL4" t="inlineStr"/>
       <c r="BM4" t="n">
-        <v>163018000</v>
+        <v>217657000</v>
       </c>
       <c r="BN4" t="n">
-        <v>129964000</v>
+        <v>196985000</v>
       </c>
       <c r="BO4" t="n">
-        <v>33054000</v>
+        <v>20672000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
         <v>212187488</v>
@@ -2167,45 +2165,43 @@
         <v>212187488</v>
       </c>
       <c r="D5" t="n">
-        <v>129366000</v>
+        <v>114257000</v>
       </c>
       <c r="E5" t="n">
-        <v>380076000</v>
+        <v>421892000</v>
       </c>
       <c r="F5" t="n">
-        <v>440303000</v>
+        <v>454940000</v>
       </c>
       <c r="G5" t="n">
-        <v>27219000</v>
+        <v>130391000</v>
       </c>
       <c r="H5" t="n">
-        <v>380076000</v>
+        <v>421892000</v>
       </c>
       <c r="I5" t="n">
-        <v>113846000</v>
+        <v>114257000</v>
       </c>
       <c r="J5" t="n">
-        <v>424783000</v>
+        <v>454940000</v>
       </c>
       <c r="K5" t="n">
-        <v>424783000</v>
+        <v>454940000</v>
       </c>
       <c r="L5" t="n">
-        <v>424783000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
+        <v>454940000</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>424783000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>6366000</v>
-      </c>
+        <v>454940000</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>125729000</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+        <v>193160000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>189699000</v>
+      </c>
       <c r="R5" t="n">
         <v>21219000</v>
       </c>
@@ -2213,141 +2209,145 @@
         <v>21219000</v>
       </c>
       <c r="T5" t="n">
-        <v>360094000</v>
+        <v>377626000</v>
       </c>
       <c r="U5" t="n">
-        <v>93297000</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
+        <v>94838000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>262000</v>
+      </c>
       <c r="W5" t="n">
-        <v>3738000</v>
+        <v>5014000</v>
       </c>
       <c r="X5" t="n">
-        <v>1570000</v>
+        <v>1242000</v>
       </c>
       <c r="Y5" t="n">
-        <v>87989000</v>
+        <v>88320000</v>
       </c>
       <c r="Z5" t="n">
-        <v>87989000</v>
+        <v>88320000</v>
       </c>
       <c r="AA5" t="n">
-        <v>266797000</v>
+        <v>282788000</v>
       </c>
       <c r="AB5" t="n">
-        <v>41377000</v>
+        <v>25937000</v>
       </c>
       <c r="AC5" t="n">
-        <v>25857000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>15520000</v>
-      </c>
+        <v>25937000</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>58308000</v>
+        <v>80211000</v>
       </c>
       <c r="AF5" t="n">
-        <v>35748000</v>
+        <v>38472000</v>
       </c>
       <c r="AG5" t="n">
-        <v>2893000</v>
+        <v>8236000</v>
       </c>
       <c r="AH5" t="n">
-        <v>19667000</v>
+        <v>33503000</v>
       </c>
       <c r="AI5" t="n">
-        <v>784877000</v>
+        <v>832566000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>490861000</v>
+        <v>419387000</v>
       </c>
       <c r="AK5" t="n">
-        <v>2698000</v>
+        <v>8094000</v>
       </c>
       <c r="AL5" t="n">
-        <v>82976000</v>
+        <v>70077000</v>
       </c>
       <c r="AM5" t="n">
-        <v>44707000</v>
+        <v>33048000</v>
       </c>
       <c r="AN5" t="n">
-        <v>44707000</v>
+        <v>33048000</v>
       </c>
       <c r="AO5" t="n">
-        <v>355024000</v>
+        <v>301986000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-286148000</v>
+        <v>-276387000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>641172000</v>
+        <v>578373000</v>
       </c>
       <c r="AR5" t="n">
-        <v>89000</v>
+        <v>270000</v>
       </c>
       <c r="AS5" t="n">
-        <v>1155000</v>
+        <v>1261000</v>
       </c>
       <c r="AT5" t="n">
-        <v>184947000</v>
+        <v>152643000</v>
       </c>
       <c r="AU5" t="n">
-        <v>454981000</v>
+        <v>424199000</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>294016000</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>550000</v>
-      </c>
+        <v>413179000</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>641000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>12411000</v>
+        <v>6011000</v>
       </c>
       <c r="BA5" t="n">
-        <v>51306000</v>
+        <v>49515000</v>
       </c>
       <c r="BB5" t="n">
-        <v>-15809000</v>
+        <v>-31899000</v>
       </c>
       <c r="BC5" t="n">
-        <v>28192000</v>
+        <v>48659000</v>
       </c>
       <c r="BD5" t="n">
-        <v>6956000</v>
+        <v>5715000</v>
       </c>
       <c r="BE5" t="n">
-        <v>31967000</v>
+        <v>27040000</v>
       </c>
       <c r="BF5" t="n">
-        <v>7820000</v>
+        <v>18773000</v>
       </c>
       <c r="BG5" t="n">
-        <v>6532000</v>
+        <v>623000</v>
       </c>
       <c r="BH5" t="n">
-        <v>36141000</v>
+        <v>72030000</v>
       </c>
       <c r="BI5" t="n">
-        <v>-3541000</v>
+        <v>-7749000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>39682000</v>
+        <v>79779000</v>
       </c>
       <c r="BK5" t="n">
-        <v>178173000</v>
-      </c>
-      <c r="BL5" t="inlineStr"/>
+        <v>263323000</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>129551000</v>
+      </c>
       <c r="BM5" t="n">
-        <v>178173000</v>
-      </c>
-      <c r="BN5" t="inlineStr"/>
-      <c r="BO5" t="inlineStr"/>
+        <v>133772000</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>105592000</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>28180000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2612,568 +2612,568 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>90634000</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+        <v>82363000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-38790000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23250000</v>
+      </c>
       <c r="E2" t="n">
-        <v>-18529000</v>
+        <v>-15871000</v>
       </c>
       <c r="F2" t="n">
-        <v>133772000</v>
+        <v>178173000</v>
       </c>
       <c r="G2" t="n">
-        <v>217657000</v>
+        <v>136036000</v>
       </c>
       <c r="H2" t="n">
-        <v>-1677000</v>
+        <v>6947000</v>
       </c>
       <c r="I2" t="n">
-        <v>-82208000</v>
+        <v>35190000</v>
       </c>
       <c r="J2" t="n">
-        <v>-49817000</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
+        <v>-48846000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-5000</v>
+      </c>
       <c r="L2" t="n">
-        <v>-4660000</v>
+        <v>-3393000</v>
       </c>
       <c r="M2" t="n">
-        <v>-19132000</v>
+        <v>-70000</v>
       </c>
       <c r="N2" t="n">
-        <v>-19132000</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+        <v>-70000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-15540000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-15540000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-38790000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>23250000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-15540000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-38790000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>23250000</v>
+      </c>
       <c r="V2" t="n">
-        <v>-141554000</v>
+        <v>-14198000</v>
       </c>
       <c r="W2" t="n">
-        <v>6492000</v>
+        <v>927000</v>
       </c>
       <c r="X2" t="n">
-        <v>-129551000</v>
+        <v>741000</v>
       </c>
       <c r="Y2" t="n">
+        <v>741000</v>
+      </c>
+      <c r="Z2" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" t="n">
-        <v>-129551000</v>
-      </c>
       <c r="AA2" t="n">
-        <v>-2844000</v>
+        <v>-1951000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-2844000</v>
+        <v>-1951000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-15651000</v>
+        <v>-13915000</v>
       </c>
       <c r="AD2" t="n">
-        <v>34000</v>
+        <v>5000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-15685000</v>
+        <v>-13920000</v>
       </c>
       <c r="AF2" t="n">
-        <v>109163000</v>
+        <v>98234000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-1081000</v>
+        <v>3072000</v>
       </c>
       <c r="AH2" t="n">
-        <v>222000</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
+        <v>106000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-292000</v>
+      </c>
       <c r="AJ2" t="n">
-        <v>2018000</v>
+        <v>9475000</v>
       </c>
       <c r="AK2" t="n">
-        <v>19220000</v>
+        <v>-8182000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-645000</v>
+        <v>6000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-11063000</v>
+        <v>9011000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-5494000</v>
+        <v>8640000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-2231000</v>
+        <v>2569000</v>
       </c>
       <c r="AP2" t="n">
-        <v>8604000</v>
+        <v>3257000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>46366000</v>
+        <v>58459000</v>
       </c>
       <c r="AR2" t="n">
-        <v>3123000</v>
+        <v>4849000</v>
       </c>
       <c r="AS2" t="n">
-        <v>43243000</v>
+        <v>53610000</v>
       </c>
       <c r="AT2" t="n">
-        <v>462000</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
+        <v>-225000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>-1384000</v>
+      </c>
       <c r="AV2" t="n">
-        <v>6423000</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
+        <v>-2000</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>-6816000</v>
+      </c>
       <c r="AX2" t="n">
-        <v>47788000</v>
+        <v>16548000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>55309000</v>
+        <v>71938000</v>
       </c>
       <c r="C3" t="n">
+        <v>-15520000</v>
+      </c>
+      <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>-13453000</v>
+        <v>-13538000</v>
       </c>
       <c r="F3" t="n">
-        <v>217657000</v>
+        <v>163018000</v>
       </c>
       <c r="G3" t="n">
-        <v>163018000</v>
+        <v>178173000</v>
       </c>
       <c r="H3" t="n">
-        <v>1611000</v>
+        <v>-7060000</v>
       </c>
       <c r="I3" t="n">
-        <v>53028000</v>
+        <v>-8095000</v>
       </c>
       <c r="J3" t="n">
-        <v>-42031000</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-196000</v>
-      </c>
+        <v>-51172000</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-3466000</v>
+        <v>-2966000</v>
       </c>
       <c r="M3" t="n">
-        <v>-12731000</v>
+        <v>-6314000</v>
       </c>
       <c r="N3" t="n">
-        <v>-12731000</v>
+        <v>-6314000</v>
       </c>
       <c r="O3" t="n">
+        <v>-15520000</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-15520000</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-15520000</v>
+      </c>
+      <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-15520000</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-15520000</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>26297000</v>
+        <v>-42399000</v>
       </c>
       <c r="W3" t="n">
-        <v>3491000</v>
+        <v>1164000</v>
       </c>
       <c r="X3" t="n">
-        <v>34134000</v>
+        <v>-30289000</v>
       </c>
       <c r="Y3" t="n">
-        <v>34134000</v>
+        <v>2450000</v>
       </c>
       <c r="Z3" t="n">
+        <v>-32739000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-1441000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-1441000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-11833000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>264000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-12097000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>85476000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-350000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>22000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-36000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-879000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>16072000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>852000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-8256000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>-9547000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1756000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>4928000</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>53803000</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4331000</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>49472000</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>335000</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>-3885000</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>11000</v>
+      </c>
+      <c r="AW3" t="n">
         <v>0</v>
       </c>
-      <c r="AA3" t="n">
-        <v>-1930000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-1930000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-9398000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>2125000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-11523000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>68762000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1720000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>-34090000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>-15746000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>-204000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>5162000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>-23302000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>-85000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>8858000</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>49285000</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>3783000</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>45502000</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>406000</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>590000</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>-86000</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>40012000</v>
+        <v>26382000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>71938000</v>
+        <v>55309000</v>
       </c>
       <c r="C4" t="n">
-        <v>-15520000</v>
-      </c>
-      <c r="D4" t="n">
         <v>0</v>
       </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>-13538000</v>
+        <v>-13453000</v>
       </c>
       <c r="F4" t="n">
+        <v>217657000</v>
+      </c>
+      <c r="G4" t="n">
         <v>163018000</v>
       </c>
-      <c r="G4" t="n">
-        <v>178173000</v>
-      </c>
       <c r="H4" t="n">
-        <v>-7060000</v>
+        <v>1611000</v>
       </c>
       <c r="I4" t="n">
-        <v>-8095000</v>
+        <v>53028000</v>
       </c>
       <c r="J4" t="n">
-        <v>-51172000</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
+        <v>-42031000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-196000</v>
+      </c>
       <c r="L4" t="n">
-        <v>-2966000</v>
+        <v>-3466000</v>
       </c>
       <c r="M4" t="n">
-        <v>-6314000</v>
+        <v>-12731000</v>
       </c>
       <c r="N4" t="n">
-        <v>-6314000</v>
+        <v>-12731000</v>
       </c>
       <c r="O4" t="n">
-        <v>-15520000</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-15520000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-15520000</v>
-      </c>
-      <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>-15520000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-15520000</v>
+        <v>0</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-42399000</v>
+        <v>26297000</v>
       </c>
       <c r="W4" t="n">
-        <v>1164000</v>
+        <v>3491000</v>
       </c>
       <c r="X4" t="n">
-        <v>-30289000</v>
+        <v>34134000</v>
       </c>
       <c r="Y4" t="n">
-        <v>2450000</v>
+        <v>34134000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-32739000</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1441000</v>
+        <v>-1930000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-1441000</v>
+        <v>-1930000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-11833000</v>
+        <v>-9398000</v>
       </c>
       <c r="AD4" t="n">
-        <v>264000</v>
+        <v>2125000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-12097000</v>
+        <v>-11523000</v>
       </c>
       <c r="AF4" t="n">
-        <v>85476000</v>
+        <v>68762000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-350000</v>
+        <v>1720000</v>
       </c>
       <c r="AH4" t="n">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>-36000</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-879000</v>
+        <v>-34090000</v>
       </c>
       <c r="AK4" t="n">
-        <v>16072000</v>
+        <v>-15746000</v>
       </c>
       <c r="AL4" t="n">
-        <v>852000</v>
+        <v>-204000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-8256000</v>
+        <v>5162000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-9547000</v>
+        <v>-23302000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1756000</v>
+        <v>-85000</v>
       </c>
       <c r="AP4" t="n">
-        <v>4928000</v>
+        <v>8858000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>53803000</v>
+        <v>49285000</v>
       </c>
       <c r="AR4" t="n">
-        <v>4331000</v>
+        <v>3783000</v>
       </c>
       <c r="AS4" t="n">
-        <v>49472000</v>
+        <v>45502000</v>
       </c>
       <c r="AT4" t="n">
-        <v>335000</v>
+        <v>406000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-3885000</v>
+        <v>590000</v>
       </c>
       <c r="AV4" t="n">
-        <v>11000</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
+        <v>-86000</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>26382000</v>
+        <v>40012000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>82363000</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-38790000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>23250000</v>
-      </c>
+        <v>90634000</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>-15871000</v>
+        <v>-18529000</v>
       </c>
       <c r="F5" t="n">
-        <v>178173000</v>
+        <v>133772000</v>
       </c>
       <c r="G5" t="n">
-        <v>136036000</v>
+        <v>217657000</v>
       </c>
       <c r="H5" t="n">
-        <v>6947000</v>
+        <v>-1677000</v>
       </c>
       <c r="I5" t="n">
-        <v>35190000</v>
+        <v>-82208000</v>
       </c>
       <c r="J5" t="n">
-        <v>-48846000</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-5000</v>
-      </c>
+        <v>-49817000</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>-3393000</v>
+        <v>-4660000</v>
       </c>
       <c r="M5" t="n">
-        <v>-70000</v>
+        <v>-19132000</v>
       </c>
       <c r="N5" t="n">
-        <v>-70000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-15540000</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-15540000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-38790000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>23250000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-15540000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-38790000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>23250000</v>
-      </c>
+        <v>-19132000</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-14198000</v>
+        <v>-141554000</v>
       </c>
       <c r="W5" t="n">
-        <v>927000</v>
+        <v>6492000</v>
       </c>
       <c r="X5" t="n">
-        <v>741000</v>
+        <v>-129551000</v>
       </c>
       <c r="Y5" t="n">
-        <v>741000</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-129551000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-1951000</v>
+        <v>-2844000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1951000</v>
+        <v>-2844000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-13915000</v>
+        <v>-15651000</v>
       </c>
       <c r="AD5" t="n">
-        <v>5000</v>
+        <v>34000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-13920000</v>
+        <v>-15685000</v>
       </c>
       <c r="AF5" t="n">
-        <v>98234000</v>
+        <v>109163000</v>
       </c>
       <c r="AG5" t="n">
-        <v>3072000</v>
+        <v>-1081000</v>
       </c>
       <c r="AH5" t="n">
-        <v>106000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-292000</v>
-      </c>
+        <v>222000</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>9475000</v>
+        <v>2018000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-8182000</v>
+        <v>19220000</v>
       </c>
       <c r="AL5" t="n">
-        <v>6000</v>
+        <v>-645000</v>
       </c>
       <c r="AM5" t="n">
-        <v>9011000</v>
+        <v>-11063000</v>
       </c>
       <c r="AN5" t="n">
-        <v>8640000</v>
+        <v>-5494000</v>
       </c>
       <c r="AO5" t="n">
-        <v>2569000</v>
+        <v>-2231000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3257000</v>
+        <v>8604000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>58459000</v>
+        <v>46366000</v>
       </c>
       <c r="AR5" t="n">
-        <v>4849000</v>
+        <v>3123000</v>
       </c>
       <c r="AS5" t="n">
-        <v>53610000</v>
+        <v>43243000</v>
       </c>
       <c r="AT5" t="n">
-        <v>-225000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>-1384000</v>
-      </c>
+        <v>462000</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>-2000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>-6816000</v>
-      </c>
+        <v>6423000</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>16548000</v>
+        <v>47788000</v>
       </c>
     </row>
   </sheetData>
@@ -3738,187 +3738,187 @@
       </c>
       <c r="DF1" t="inlineStr">
         <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>longName</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
       <c r="EQ1" t="inlineStr">
@@ -4021,34 +4021,34 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="V2" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="W2" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="X2" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AC2" t="n">
         <v>0.12</v>
       </c>
       <c r="AD2" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="AE2" t="n">
         <v>1765238400</v>
@@ -4060,31 +4060,31 @@
         <v>3.87</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.239</v>
+        <v>0.228</v>
       </c>
       <c r="AI2" t="n">
-        <v>7.3</v>
+        <v>7.7999997</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="AL2" t="n">
-        <v>11800</v>
+        <v>11915</v>
       </c>
       <c r="AM2" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
@@ -4093,13 +4093,13 @@
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>309793728</v>
+        <v>331012480</v>
       </c>
       <c r="AT2" t="n">
-        <v>305549982</v>
+        <v>331012481</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AV2" t="n">
         <v>2</v>
@@ -4111,19 +4111,19 @@
         <v>0.53</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.46943137</v>
+        <v>0.50158423</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.6064</v>
+        <v>1.5714</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.75035</v>
+        <v>1.7529</v>
       </c>
       <c r="BB2" t="n">
         <v>0.12</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.08333333</v>
+        <v>0.08219178000000001</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>158916736</v>
+        <v>180135488</v>
       </c>
       <c r="BG2" t="n">
         <v>0.06329</v>
@@ -4158,7 +4158,7 @@
         <v>2.245</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.6503341</v>
+        <v>0.6948775</v>
       </c>
       <c r="BO2" t="n">
         <v>1751241600</v>
@@ -4182,16 +4182,16 @@
         <v>0.51</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.241</v>
+        <v>0.273</v>
       </c>
       <c r="BW2" t="n">
-        <v>2.48</v>
+        <v>2.811</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.06666672</v>
+        <v>0.09859156600000001</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BZ2" t="n">
         <v>0.12</v>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="CC2" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
@@ -4307,140 +4307,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DF2" t="n">
+        <v>6.8493085</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>TAI PING CARPET</t>
+        </is>
+      </c>
+      <c r="DJ2" t="n">
+        <v>0.099999905</v>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>1.56 - 1.56</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DM2" t="n">
+        <v>11915</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0.13999999</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0.098591544</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>1.42 - 2.0</t>
+        </is>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.44000006</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.22000003</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>9.859157</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>1739967022</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1739967022</v>
+      </c>
+      <c r="DV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>-0.011400104</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-0.007254743</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-0.19290006</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>-0.110046245</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>15</v>
+      </c>
+      <c r="ED2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>947035800000</v>
+      </c>
+      <c r="EG2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DG2" t="n">
-        <v>1780276821</v>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DI2" t="inlineStr">
+      <c r="EH2" t="n">
+        <v>1780455665</v>
+      </c>
+      <c r="EI2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="EJ2" t="inlineStr">
         <is>
           <t>finmb_877162</t>
         </is>
       </c>
-      <c r="DK2" t="inlineStr">
+      <c r="EK2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DL2" t="inlineStr">
+      <c r="EL2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DM2" t="n">
+      <c r="EM2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DN2" t="inlineStr">
+      <c r="EN2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
-      </c>
-      <c r="DO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>Tai Ping Carpets International Limited</t>
-        </is>
-      </c>
-      <c r="DQ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>1.3888875</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>TAI PING CARPET</t>
-        </is>
-      </c>
-      <c r="DU2" t="n">
-        <v>0.01999998</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>1.44 - 1.44</t>
-        </is>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DX2" t="n">
-        <v>11800</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>0.110000014</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>0.081481494</v>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>1.35 - 2.0</t>
-        </is>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.5399999599999999</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>-0.26999998</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>6.666672</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>1739967022</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>1739967022</v>
-      </c>
-      <c r="EG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>-0.14639997</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>-0.09113544</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>-0.29034996</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>-0.16588108</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>15</v>
       </c>
       <c r="EO2" t="b">
         <v>0</v>
       </c>
-      <c r="EP2" t="n">
-        <v>947035800000</v>
+      <c r="EP2" t="inlineStr">
+        <is>
+          <t>Tai Ping Carpets International Limited</t>
+        </is>
       </c>
       <c r="EQ2" t="inlineStr"/>
     </row>
